--- a/modulos/rutinas/Excel_Solo_Valores.xlsx
+++ b/modulos/rutinas/Excel_Solo_Valores.xlsx
@@ -432,13 +432,13 @@
         <v>AA NP</v>
       </c>
       <c r="E1" t="str">
-        <v>73.5</v>
+        <v>73.4</v>
       </c>
       <c r="F1" t="str">
         <v>AA</v>
       </c>
       <c r="G1" t="str">
-        <v>67.5</v>
+        <v>67.4</v>
       </c>
       <c r="H1" t="str">
         <v>70.97%</v>
@@ -1450,10 +1450,10 @@
         <v>Valor decimal</v>
       </c>
       <c r="F36">
-        <v>0.7000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="G36">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="H36" t="str">
         <v/>
@@ -1511,7 +1511,7 @@
         <v>1.5</v>
       </c>
       <c r="G38">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -1609,19 +1609,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Kato</v>
+        <v>Balleston aleman braq</v>
       </c>
       <c r="B42">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="E42">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F42" t="str">
         <v/>
@@ -2009,13 +2009,13 @@
         <v>AA NP</v>
       </c>
       <c r="E1" t="str">
-        <v>74.6</v>
+        <v>74.9</v>
       </c>
       <c r="F1" t="str">
         <v>AA</v>
       </c>
       <c r="G1" t="str">
-        <v>70.1</v>
+        <v>70.4</v>
       </c>
       <c r="H1" t="str">
         <v>72.46%</v>
@@ -3078,7 +3078,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Kip</v>
+        <v>Kip L</v>
       </c>
       <c r="B24">
         <v>8</v>
@@ -3125,19 +3125,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dislocada</v>
+        <v>Kato</v>
       </c>
       <c r="B25">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E25">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F25">
         <v>1.4</v>
@@ -3172,19 +3172,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Deltchev</v>
+        <v>Gigante sost</v>
       </c>
       <c r="B26">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E26">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -3219,19 +3219,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Dominada adelante a Lsit</v>
+        <v>Dislocada</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="E27">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Escuadra Rusa</v>
+        <v>Deltchev</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="str">
         <v>B</v>
@@ -3313,13 +3313,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Kato</v>
+        <v>Dominada adelante a Lsit</v>
       </c>
       <c r="B29">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="str">
         <v>B</v>
@@ -3360,19 +3360,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Gigante sost</v>
+        <v>Escuadra Rusa</v>
       </c>
       <c r="B30">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="E30">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F30" t="str">
         <v/>
@@ -4127,10 +4127,10 @@
         <v>Valor decimal</v>
       </c>
       <c r="F46">
-        <v>1.5</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="G46">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -4224,7 +4224,7 @@
         <v>1.7</v>
       </c>
       <c r="G48">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="H48">
         <v>0.9</v>
@@ -4300,19 +4300,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Gigante</v>
+        <v>Adler</v>
       </c>
       <c r="B50">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="E50">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F50" t="str">
         <v/>
@@ -4347,19 +4347,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Cambio directo</v>
+        <v>Molino cubital</v>
       </c>
       <c r="B51">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E51">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F51" t="str">
         <v/>
@@ -5674,7 +5674,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Kip</v>
+        <v>Kip L</v>
       </c>
       <c r="B25">
         <v>8</v>
@@ -14710,13 +14710,13 @@
         <v>AA NP</v>
       </c>
       <c r="E1" t="str">
-        <v>88.2</v>
+        <v>88.7</v>
       </c>
       <c r="F1" t="str">
         <v>AA</v>
       </c>
       <c r="G1" t="str">
-        <v>79.4</v>
+        <v>79.9</v>
       </c>
       <c r="H1" t="str">
         <v>80.95%</v>
@@ -14771,10 +14771,10 @@
         <v>Valor decimal</v>
       </c>
       <c r="F3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G3">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -14832,7 +14832,7 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="H5">
         <v>0.85</v>
@@ -14872,19 +14872,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Doble giro atrás LC</v>
+        <v>Doble giro extendido adel LC</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>4</v>
       </c>
       <c r="D7" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="E7">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -14959,10 +14959,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Doble giro extendido adel</v>
+        <v>Doble giro y medio atras</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -16105,10 +16105,10 @@
         <v>Valor decimal</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G49">
-        <v>15</v>
+        <v>15.399999999999999</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -16166,7 +16166,7 @@
         <v>2</v>
       </c>
       <c r="G51">
-        <v>13.5</v>
+        <v>13.899999999999999</v>
       </c>
       <c r="H51">
         <v>0.7</v>
@@ -16362,8 +16362,8 @@
       <c r="D58" t="str">
         <v>BPC</v>
       </c>
-      <c r="E58" t="str">
-        <v/>
+      <c r="E58">
+        <v>0.2</v>
       </c>
       <c r="F58" t="str">
         <v/>
@@ -16633,7 +16633,7 @@
         <v>Fedorchenko</v>
       </c>
       <c r="O5" t="str">
-        <v>Doble giro atrás LC</v>
+        <v>Doble giro extendido adel LC</v>
       </c>
       <c r="P5" t="str">
         <v/>
@@ -16783,7 +16783,7 @@
         <v>Mortal Ext ade</v>
       </c>
       <c r="O8" t="str">
-        <v>Doble giro extendido adel</v>
+        <v>Doble giro y medio atras</v>
       </c>
       <c r="P8" t="str">
         <v/>
@@ -17271,7 +17271,7 @@
         <v>Inglesa a cristo</v>
       </c>
       <c r="K18" t="str">
-        <v>Kip</v>
+        <v>Kip L</v>
       </c>
       <c r="L18" t="str">
         <v>Kip cristo</v>
@@ -17321,10 +17321,10 @@
         <v>Cristo ascenso apoyo en L</v>
       </c>
       <c r="K19" t="str">
-        <v>Dislocada</v>
+        <v>Kato</v>
       </c>
       <c r="L19" t="str">
-        <v>Kip</v>
+        <v>Kip L</v>
       </c>
       <c r="M19" t="str">
         <v>Plancha dorsal</v>
@@ -17371,7 +17371,7 @@
         <v>Inglesa</v>
       </c>
       <c r="K20" t="str">
-        <v>Deltchev</v>
+        <v>Gigante sost</v>
       </c>
       <c r="L20" t="str">
         <v>Kato 3"</v>
@@ -17421,7 +17421,7 @@
         <v>L sit</v>
       </c>
       <c r="K21" t="str">
-        <v>Dominada adelante a Lsit</v>
+        <v>Dislocada</v>
       </c>
       <c r="L21" t="str">
         <v>Gigante Pas</v>
@@ -17471,7 +17471,7 @@
         <v>Kato</v>
       </c>
       <c r="K22" t="str">
-        <v>Escuadra Rusa</v>
+        <v>Deltchev</v>
       </c>
       <c r="L22" t="str">
         <v>Gigante sost</v>
@@ -17521,7 +17521,7 @@
         <v>Molino Sostenido</v>
       </c>
       <c r="K23" t="str">
-        <v>Kato</v>
+        <v>Dominada adelante a Lsit</v>
       </c>
       <c r="L23" t="str">
         <v>Molino pas</v>
@@ -17571,7 +17571,7 @@
         <v>Gigante Pas</v>
       </c>
       <c r="K24" t="str">
-        <v>Gigante sost</v>
+        <v>Escuadra Rusa</v>
       </c>
       <c r="L24" t="str">
         <v>Molino sost</v>
@@ -17647,7 +17647,7 @@
         <v>Tsukahara en C</v>
       </c>
       <c r="C26" t="str">
-        <v>Tsukahara en C</v>
+        <v>Resorte</v>
       </c>
       <c r="D26" t="str">
         <v>Tsukahara en carpa</v>
@@ -17797,7 +17797,7 @@
         <v>Vuelo</v>
       </c>
       <c r="C29" t="str">
-        <v>L-sit</v>
+        <v>Moy extendido</v>
       </c>
       <c r="D29" t="str">
         <v>L-sit</v>
@@ -17847,7 +17847,7 @@
         <v xml:space="preserve">Braq Subida de pecho </v>
       </c>
       <c r="C30" t="str">
-        <v>Kato</v>
+        <v>L-sit</v>
       </c>
       <c r="D30" t="str">
         <v>Kato</v>
@@ -17897,7 +17897,7 @@
         <v>Vuelo</v>
       </c>
       <c r="C31" t="str">
-        <v xml:space="preserve">Braq Subida de pecho </v>
+        <v>Rusa</v>
       </c>
       <c r="D31" t="str">
         <v xml:space="preserve">Braq Subida de pecho </v>
@@ -17947,7 +17947,7 @@
         <v>L-sit</v>
       </c>
       <c r="C32" t="str">
-        <v>Vuelo</v>
+        <v>Kato</v>
       </c>
       <c r="D32" t="str">
         <v>Vuelo</v>
@@ -17994,10 +17994,10 @@
         <v/>
       </c>
       <c r="B33" t="str">
-        <v>Kato</v>
+        <v>Balleston aleman braq</v>
       </c>
       <c r="C33" t="str">
-        <v>Moy extendido</v>
+        <v xml:space="preserve">Braq Subida de pecho </v>
       </c>
       <c r="D33" t="str">
         <v>Moy braquial</v>
@@ -18047,7 +18047,7 @@
         <v>Vuelo</v>
       </c>
       <c r="C34" t="str">
-        <v>Rusa</v>
+        <v>Vuelo</v>
       </c>
       <c r="D34" t="str">
         <v>Inglesa</v>
@@ -18162,7 +18162,7 @@
         <v>Voronin</v>
       </c>
       <c r="H36" t="str">
-        <v>Alemana</v>
+        <v/>
       </c>
       <c r="I36" t="str">
         <v>Gienger</v>
@@ -18212,7 +18212,7 @@
         <v>Alemana a manos</v>
       </c>
       <c r="H37" t="str">
-        <v>Gigante</v>
+        <v/>
       </c>
       <c r="I37" t="str">
         <v>Alemana a manos</v>
@@ -18262,7 +18262,7 @@
         <v>Gigante</v>
       </c>
       <c r="H38" t="str">
-        <v>Gigante Saltado</v>
+        <v/>
       </c>
       <c r="I38" t="str">
         <v>Gigante</v>
@@ -18312,7 +18312,7 @@
         <v>Gigante Saltado</v>
       </c>
       <c r="H39" t="str">
-        <v>Salvada</v>
+        <v/>
       </c>
       <c r="I39" t="str">
         <v>Salvada</v>
@@ -18321,7 +18321,7 @@
         <v>Endo</v>
       </c>
       <c r="K39" t="str">
-        <v>Gigante</v>
+        <v>Adler</v>
       </c>
       <c r="L39" t="str">
         <v>Gigante</v>
@@ -18362,7 +18362,7 @@
         <v>Cambio directo</v>
       </c>
       <c r="H40" t="str">
-        <v>Cambio directo</v>
+        <v/>
       </c>
       <c r="I40" t="str">
         <v>Cambio directo</v>
@@ -18371,7 +18371,7 @@
         <v>Endo cerrado</v>
       </c>
       <c r="K40" t="str">
-        <v>Cambio directo</v>
+        <v>Molino cubital</v>
       </c>
       <c r="L40" t="str">
         <v>Cambio directo</v>
@@ -18412,7 +18412,7 @@
         <v>Molino</v>
       </c>
       <c r="H41" t="str">
-        <v>Molino</v>
+        <v/>
       </c>
       <c r="I41" t="str">
         <v>Molino</v>
@@ -18462,7 +18462,7 @@
         <v>Cambio sencillo</v>
       </c>
       <c r="H42" t="str">
-        <v>Cambio sencillo</v>
+        <v/>
       </c>
       <c r="I42" t="str">
         <v>Cambio sencillo</v>
@@ -18512,7 +18512,7 @@
         <v>Doble agrupado atras</v>
       </c>
       <c r="H43" t="str">
-        <v>Doble agrupado atras</v>
+        <v/>
       </c>
       <c r="I43" t="str">
         <v>Multiple extendido atras</v>
@@ -19187,7 +19187,7 @@
         <v>DIEGO J</v>
       </c>
       <c r="B2">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="C2">
         <v>15</v>
@@ -19202,10 +19202,10 @@
         <v>14.9</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>15.399999999999999</v>
       </c>
       <c r="H2">
-        <v>79.4</v>
+        <v>79.9</v>
       </c>
     </row>
     <row r="3">
@@ -19306,10 +19306,10 @@
         <v>12.9</v>
       </c>
       <c r="G6">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="H6">
-        <v>70.1</v>
+        <v>70.4</v>
       </c>
     </row>
     <row r="7">
@@ -19384,10 +19384,10 @@
         <v>12.299999999999999</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="H9">
-        <v>64.7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -19430,7 +19430,7 @@
         <v>12.5</v>
       </c>
       <c r="E11">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="F11">
         <v>12.7</v>
@@ -19439,7 +19439,7 @@
         <v>11.799999999999999</v>
       </c>
       <c r="H11">
-        <v>66.5</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="12">
@@ -19537,13 +19537,13 @@
         <v>12.2</v>
       </c>
       <c r="F15">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="G15">
         <v>12.1</v>
       </c>
       <c r="H15">
-        <v>67.5</v>
+        <v>67.4</v>
       </c>
     </row>
   </sheetData>
@@ -19585,7 +19585,7 @@
         <v>DIEGO J</v>
       </c>
       <c r="B2">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="C2">
         <v>3.0000000000000004</v>
@@ -19600,7 +19600,7 @@
         <v>2.9</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -19692,7 +19692,7 @@
         <v>1.5</v>
       </c>
       <c r="G6">
-        <v>1.5</v>
+        <v>1.7999999999999998</v>
       </c>
     </row>
     <row r="7">
@@ -19801,10 +19801,10 @@
         <v>0.8999999999999999</v>
       </c>
       <c r="E11">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="F11">
-        <v>1.0999999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="G11">
         <v>0.7</v>
@@ -19896,7 +19896,7 @@
         <v>2.2</v>
       </c>
       <c r="F15">
-        <v>0.7000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="G15">
         <v>0.6</v>
@@ -20117,7 +20117,7 @@
         <v>1.2</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="10">
@@ -20286,13 +20286,13 @@
         <v>AA NP</v>
       </c>
       <c r="F1" t="str">
-        <v>75.3</v>
+        <v>74.3</v>
       </c>
       <c r="G1" t="str">
         <v>AA</v>
       </c>
       <c r="H1" t="str">
-        <v>66.5</v>
+        <v>65.5</v>
       </c>
       <c r="I1" t="str">
         <v>77.07%</v>
@@ -22020,7 +22020,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Tsukahara en C</v>
+        <v>Resorte</v>
       </c>
       <c r="B34">
         <v>307</v>
@@ -22029,16 +22029,16 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="G34">
-        <v>10.899999999999999</v>
+        <v>9.899999999999999</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -22144,7 +22144,7 @@
         <v>REQUISITO</v>
       </c>
       <c r="G36">
-        <v>1.0999999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="H36">
         <v>12.7</v>
@@ -22232,22 +22232,22 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>L-sit</v>
+        <v>Moy extendido</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="E38">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F38" t="str">
-        <v>II</v>
+        <v>III</v>
       </c>
       <c r="G38">
         <v>1.6</v>
@@ -22285,19 +22285,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Kato</v>
+        <v>L-sit</v>
       </c>
       <c r="B39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="D39" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="E39">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F39" t="str">
         <v>II</v>
@@ -22338,13 +22338,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">Braq Subida de pecho </v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
+        <v>Rusa</v>
+      </c>
+      <c r="B40" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C40" t="str">
+        <v>X</v>
       </c>
       <c r="D40" t="str">
         <v>A</v>
@@ -22353,7 +22353,7 @@
         <v>0.1</v>
       </c>
       <c r="F40" t="str">
-        <v>I</v>
+        <v>EV</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -22391,19 +22391,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Vuelo</v>
+        <v>Kato</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
       <c r="D41" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E41">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F41" t="str">
         <v>II</v>
@@ -22444,22 +22444,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Moy extendido</v>
+        <v xml:space="preserve">Braq Subida de pecho </v>
       </c>
       <c r="B42">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="E42">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F42" t="str">
-        <v>III</v>
+        <v>I</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -22497,13 +22497,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Rusa</v>
-      </c>
-      <c r="B43" t="str">
-        <v>EV</v>
-      </c>
-      <c r="C43" t="str">
-        <v>X</v>
+        <v>Vuelo</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
       </c>
       <c r="D43" t="str">
         <v>A</v>
@@ -22512,7 +22512,7 @@
         <v>0.1</v>
       </c>
       <c r="F43" t="str">
-        <v>EV</v>
+        <v>II</v>
       </c>
       <c r="G43" t="str">
         <v>BPS</v>
@@ -25152,19 +25152,19 @@
         <v>FIJA</v>
       </c>
       <c r="C78" t="str">
-        <v>Alemana</v>
+        <v>Torera</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G78">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H78" t="str">
         <v/>
@@ -25178,13 +25178,13 @@
         <v>FIJA</v>
       </c>
       <c r="C79" t="str">
-        <v>Gigante</v>
+        <v>Alemana</v>
       </c>
       <c r="D79">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79" t="str">
         <v>A</v>
@@ -25204,19 +25204,19 @@
         <v>FIJA</v>
       </c>
       <c r="C80" t="str">
-        <v>Gigante Saltado</v>
+        <v>Gigante</v>
       </c>
       <c r="D80">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G80">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H80" t="str">
         <v/>
@@ -27960,7 +27960,7 @@
         <v>ANILLOS</v>
       </c>
       <c r="C186" t="str">
-        <v>Kip</v>
+        <v>Kip L</v>
       </c>
       <c r="D186">
         <v>8</v>
@@ -27986,19 +27986,19 @@
         <v>ANILLOS</v>
       </c>
       <c r="C187" t="str">
-        <v>Dislocada</v>
+        <v>Kato</v>
       </c>
       <c r="D187">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G187">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H187" t="str">
         <v/>
@@ -28012,19 +28012,19 @@
         <v>ANILLOS</v>
       </c>
       <c r="C188" t="str">
-        <v>Deltchev</v>
+        <v>Gigante sost</v>
       </c>
       <c r="D188">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="E188">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F188" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="G188">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H188" t="str">
         <v/>
@@ -28038,19 +28038,19 @@
         <v>ANILLOS</v>
       </c>
       <c r="C189" t="str">
-        <v>Dominada adelante a Lsit</v>
+        <v>Dislocada</v>
       </c>
       <c r="D189">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E189">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F189" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G189">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H189" t="str">
         <v/>
@@ -28064,13 +28064,13 @@
         <v>ANILLOS</v>
       </c>
       <c r="C190" t="str">
-        <v>Escuadra Rusa</v>
+        <v>Deltchev</v>
       </c>
       <c r="D190">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E190">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F190" t="str">
         <v>B</v>
@@ -28090,13 +28090,13 @@
         <v>ANILLOS</v>
       </c>
       <c r="C191" t="str">
-        <v>Kato</v>
+        <v>Dominada adelante a Lsit</v>
       </c>
       <c r="D191">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E191">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F191" t="str">
         <v>B</v>
@@ -28116,19 +28116,19 @@
         <v>ANILLOS</v>
       </c>
       <c r="C192" t="str">
-        <v>Gigante sost</v>
+        <v>Escuadra Rusa</v>
       </c>
       <c r="D192">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="E192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F192" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="G192">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H192" t="str">
         <v/>
@@ -28506,19 +28506,19 @@
         <v>FIJA</v>
       </c>
       <c r="C207" t="str">
-        <v>Gigante</v>
+        <v>Adler</v>
       </c>
       <c r="D207">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="E207">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F207" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="G207">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H207" t="str">
         <v/>
@@ -28532,19 +28532,19 @@
         <v>FIJA</v>
       </c>
       <c r="C208" t="str">
-        <v>Cambio directo</v>
+        <v>Molino cubital</v>
       </c>
       <c r="D208">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E208">
         <v>1</v>
       </c>
       <c r="F208" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G208">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H208" t="str">
         <v/>
@@ -29078,7 +29078,7 @@
         <v>ANILLOS</v>
       </c>
       <c r="C229" t="str">
-        <v>Kip</v>
+        <v>Kip L</v>
       </c>
       <c r="D229">
         <v>8</v>
@@ -31990,19 +31990,19 @@
         <v>PISO</v>
       </c>
       <c r="C341" t="str">
-        <v>Doble giro atrás LC</v>
+        <v>Doble giro extendido adel LC</v>
       </c>
       <c r="D341">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E341">
         <v>4</v>
       </c>
       <c r="F341" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="G341">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H341" t="str">
         <v/>
@@ -32068,10 +32068,10 @@
         <v>PISO</v>
       </c>
       <c r="C344" t="str">
-        <v>Doble giro extendido adel</v>
+        <v>Doble giro y medio atras</v>
       </c>
       <c r="D344">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E344">
         <v>4</v>
@@ -33628,7 +33628,7 @@
         <v>SALTO</v>
       </c>
       <c r="C404" t="str">
-        <v>Tsukahara en C</v>
+        <v>Resorte</v>
       </c>
       <c r="D404">
         <v>307</v>
@@ -33637,7 +33637,7 @@
         <v>3</v>
       </c>
       <c r="F404">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="G404">
         <v>0</v>
@@ -33706,19 +33706,19 @@
         <v>PARALELAS</v>
       </c>
       <c r="C407" t="str">
-        <v>L-sit</v>
+        <v>Moy extendido</v>
       </c>
       <c r="D407">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E407">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F407" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="G407">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H407" t="str">
         <v/>
@@ -33732,19 +33732,19 @@
         <v>PARALELAS</v>
       </c>
       <c r="C408" t="str">
-        <v>Kato</v>
+        <v>L-sit</v>
       </c>
       <c r="D408">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E408">
         <v>2</v>
       </c>
       <c r="F408" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G408">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H408" t="str">
         <v/>
@@ -33758,13 +33758,13 @@
         <v>PARALELAS</v>
       </c>
       <c r="C409" t="str">
-        <v xml:space="preserve">Braq Subida de pecho </v>
-      </c>
-      <c r="D409">
-        <v>1</v>
-      </c>
-      <c r="E409">
-        <v>1</v>
+        <v>Rusa</v>
+      </c>
+      <c r="D409" t="str">
+        <v>EV</v>
+      </c>
+      <c r="E409" t="str">
+        <v>X</v>
       </c>
       <c r="F409" t="str">
         <v>A</v>
@@ -33784,19 +33784,19 @@
         <v>PARALELAS</v>
       </c>
       <c r="C410" t="str">
-        <v>Vuelo</v>
+        <v>Kato</v>
       </c>
       <c r="D410">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E410">
         <v>2</v>
       </c>
       <c r="F410" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G410">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H410" t="str">
         <v/>
@@ -33810,19 +33810,19 @@
         <v>PARALELAS</v>
       </c>
       <c r="C411" t="str">
-        <v>Moy extendido</v>
+        <v xml:space="preserve">Braq Subida de pecho </v>
       </c>
       <c r="D411">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E411">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F411" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G411">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H411" t="str">
         <v/>
@@ -33836,13 +33836,13 @@
         <v>PARALELAS</v>
       </c>
       <c r="C412" t="str">
-        <v>Rusa</v>
-      </c>
-      <c r="D412" t="str">
-        <v>EV</v>
-      </c>
-      <c r="E412" t="str">
-        <v>X</v>
+        <v>Vuelo</v>
+      </c>
+      <c r="D412">
+        <v>1</v>
+      </c>
+      <c r="E412">
+        <v>2</v>
       </c>
       <c r="F412" t="str">
         <v>A</v>
@@ -38178,19 +38178,19 @@
         <v>PARALELAS</v>
       </c>
       <c r="C579" t="str">
-        <v>Kato</v>
+        <v>Balleston aleman braq</v>
       </c>
       <c r="D579">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="E579">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F579" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G579">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H579" t="str">
         <v/>
@@ -47088,25 +47088,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>65</v>
+      </c>
+      <c r="B1" t="str">
         <v>FER</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>__EMPTY</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>N 9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>AA NP</v>
       </c>
-      <c r="E1" t="str">
-        <v>73.5</v>
-      </c>
       <c r="F1" t="str">
+        <v>73.8</v>
+      </c>
+      <c r="G1" t="str">
         <v>AA</v>
-      </c>
-      <c r="G1" t="str">
-        <v>64.7</v>
       </c>
       <c r="H1" t="str">
         <v>76.41%</v>
@@ -47117,25 +47117,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>NP</v>
+      </c>
+      <c r="B2" t="str">
         <v>PISO</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
       <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
         <v>FER</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
         <v>NOTA D</v>
-      </c>
-      <c r="G2" t="str">
-        <v>NP</v>
       </c>
       <c r="H2" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -47145,26 +47145,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3">
+        <v>12.4</v>
+      </c>
+      <c r="B3" t="str">
         <v>NOMBRE</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>NÚM DE ID</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>GRUPO</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>VALOR</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Valor decimal</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.9999999999999998</v>
-      </c>
-      <c r="G3">
-        <v>12.4</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -47175,25 +47175,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>Probable NF</v>
+      </c>
+      <c r="B4" t="str">
         <v>Giro y medio atrás</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>9</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>4</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>C</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.3</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>GRUPOS</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Probable NF</v>
       </c>
       <c r="H4">
         <v>0.95</v>
@@ -47203,26 +47203,26 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5">
+        <v>10.9</v>
+      </c>
+      <c r="B5" t="str">
         <v>Giro atrás LC</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>9</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>4</v>
       </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <v>B</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.2</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>1.4</v>
-      </c>
-      <c r="G5">
-        <v>10.9</v>
       </c>
       <c r="H5">
         <v>0.5</v>
@@ -47233,22 +47233,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
         <v>Mortal Ext ade</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>14</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="D6" t="str">
+      <c r="E6" t="str">
         <v>B</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.2</v>
-      </c>
-      <c r="F6" t="str">
-        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -47262,22 +47262,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
         <v>Salto del tigre</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>7</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="D7" t="str">
-        <v>A</v>
-      </c>
-      <c r="E7">
+      <c r="E7" t="str">
+        <v>A</v>
+      </c>
+      <c r="F7">
         <v>0.1</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -47291,22 +47291,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
         <v>Flic facial</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>67</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="D8" t="str">
-        <v>A</v>
-      </c>
-      <c r="E8">
+      <c r="E8" t="str">
+        <v>A</v>
+      </c>
+      <c r="F8">
         <v>0.1</v>
-      </c>
-      <c r="F8" t="str">
-        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -47320,22 +47320,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v/>
+      </c>
+      <c r="B9" t="str">
         <v>Arabesca</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>61</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="D9" t="str">
-        <v>A</v>
-      </c>
-      <c r="E9">
+      <c r="E9" t="str">
+        <v>A</v>
+      </c>
+      <c r="F9">
         <v>0.1</v>
-      </c>
-      <c r="F9" t="str">
-        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -47349,25 +47349,25 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
         <v>Flick Flack</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>13</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>3</v>
       </c>
-      <c r="D10" t="str">
-        <v>A</v>
-      </c>
-      <c r="E10">
+      <c r="E10" t="str">
+        <v>A</v>
+      </c>
+      <c r="F10">
         <v>0.1</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <v>BPP</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
       </c>
       <c r="H10">
         <v>0.95</v>
@@ -47378,22 +47378,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v/>
+      </c>
+      <c r="B11" t="str">
         <v>Mortal Ext atrás</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>2</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>3</v>
       </c>
-      <c r="D11" t="str">
+      <c r="E11" t="str">
         <v>B</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.2</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -47418,11 +47418,11 @@
       <c r="D12" t="str">
         <v/>
       </c>
-      <c r="E12">
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12">
         <v>-0.3</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -47436,25 +47436,25 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
+        <v>NP</v>
+      </c>
+      <c r="B13" t="str">
         <v>ARZONES</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
       <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
         <v>FER</v>
       </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
         <v>NOTA D</v>
-      </c>
-      <c r="G13" t="str">
-        <v>NP</v>
       </c>
       <c r="H13" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -47464,26 +47464,26 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
+      <c r="A14">
+        <v>12.2</v>
+      </c>
+      <c r="B14" t="str">
         <v>NOMBRE</v>
       </c>
-      <c r="B14" t="str">
+      <c r="C14" t="str">
         <v>NÚM DE ID</v>
       </c>
-      <c r="C14" t="str">
+      <c r="D14" t="str">
         <v>GRUPO</v>
       </c>
-      <c r="D14" t="str">
+      <c r="E14" t="str">
         <v>VALOR</v>
       </c>
-      <c r="E14" t="str">
+      <c r="F14" t="str">
         <v>Valor decimal</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.9999999999999999</v>
-      </c>
-      <c r="G14">
-        <v>12.2</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -47494,25 +47494,25 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>Probable NF</v>
+      </c>
+      <c r="B15" t="str">
         <v xml:space="preserve">Corte tijera </v>
-      </c>
-      <c r="B15">
-        <v>1</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
-      <c r="D15" t="str">
-        <v>A</v>
-      </c>
-      <c r="E15">
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="str">
+        <v>A</v>
+      </c>
+      <c r="F15">
         <v>0.1</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
         <v>GRUPOS</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Probable NF</v>
       </c>
       <c r="H15">
         <v>0.85</v>
@@ -47522,26 +47522,26 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
+      <c r="A16">
+        <v>10.7</v>
+      </c>
+      <c r="B16" t="str">
         <v>Molino en arzones</v>
       </c>
-      <c r="B16">
+      <c r="C16">
         <v>1</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>2</v>
       </c>
-      <c r="D16" t="str">
-        <v>A</v>
-      </c>
-      <c r="E16">
+      <c r="E16" t="str">
+        <v>A</v>
+      </c>
+      <c r="F16">
         <v>0.1</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>1.2</v>
-      </c>
-      <c r="G16">
-        <v>10.7</v>
       </c>
       <c r="H16">
         <v>0.7</v>
@@ -47552,22 +47552,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
+        <v/>
+      </c>
+      <c r="B17" t="str">
         <v>Cheka</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>74</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>2</v>
       </c>
-      <c r="D17" t="str">
+      <c r="E17" t="str">
         <v>B</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.2</v>
-      </c>
-      <c r="F17" t="str">
-        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -47581,22 +47581,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v/>
+      </c>
+      <c r="B18" t="str">
         <v>Bajada lateral</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>1</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>3</v>
       </c>
-      <c r="D18" t="str">
-        <v>A</v>
-      </c>
-      <c r="E18">
+      <c r="E18" t="str">
+        <v>A</v>
+      </c>
+      <c r="F18">
         <v>0.1</v>
-      </c>
-      <c r="F18" t="str">
-        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -47610,22 +47610,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v/>
+      </c>
+      <c r="B19" t="str">
         <v>Molino</v>
       </c>
-      <c r="B19">
+      <c r="C19">
         <v>7</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>2</v>
       </c>
-      <c r="D19" t="str">
-        <v>A</v>
-      </c>
-      <c r="E19">
+      <c r="E19" t="str">
+        <v>A</v>
+      </c>
+      <c r="F19">
         <v>0.1</v>
-      </c>
-      <c r="F19" t="str">
-        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -47639,22 +47639,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
+        <v/>
+      </c>
+      <c r="B20" t="str">
         <v>Molino transversal</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>13</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>2</v>
       </c>
-      <c r="D20" t="str">
-        <v>A</v>
-      </c>
-      <c r="E20">
+      <c r="E20" t="str">
+        <v>A</v>
+      </c>
+      <c r="F20">
         <v>0.1</v>
-      </c>
-      <c r="F20" t="str">
-        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -47668,22 +47668,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
+        <v/>
+      </c>
+      <c r="B21" t="str">
         <v>1/2 Splindle</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>26</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>2</v>
       </c>
-      <c r="D21" t="str">
+      <c r="E21" t="str">
         <v>B</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.2</v>
-      </c>
-      <c r="F21" t="str">
-        <v/>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -47697,22 +47697,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
+        <v/>
+      </c>
+      <c r="B22" t="str">
         <v>Finlandesa</v>
       </c>
-      <c r="B22">
+      <c r="C22">
         <v>1</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>4</v>
       </c>
-      <c r="D22" t="str">
-        <v>A</v>
-      </c>
-      <c r="E22">
+      <c r="E22" t="str">
+        <v>A</v>
+      </c>
+      <c r="F22">
         <v>0.1</v>
-      </c>
-      <c r="F22" t="str">
-        <v/>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -47726,25 +47726,25 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
+        <v>NP</v>
+      </c>
+      <c r="B23" t="str">
         <v>ANILLOS</v>
       </c>
-      <c r="B23" t="str">
-        <v/>
-      </c>
       <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
         <v>FER</v>
       </c>
-      <c r="D23" t="str">
-        <v/>
-      </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
         <v>NOTA D</v>
-      </c>
-      <c r="G23" t="str">
-        <v>NP</v>
       </c>
       <c r="H23" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -47754,26 +47754,26 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
+      <c r="A24">
+        <v>12.600000000000001</v>
+      </c>
+      <c r="B24" t="str">
         <v>NOMBRE</v>
       </c>
-      <c r="B24" t="str">
+      <c r="C24" t="str">
         <v>NÚM DE ID</v>
       </c>
-      <c r="C24" t="str">
+      <c r="D24" t="str">
         <v>GRUPO</v>
       </c>
-      <c r="D24" t="str">
+      <c r="E24" t="str">
         <v>VALOR</v>
       </c>
-      <c r="E24" t="str">
+      <c r="F24" t="str">
         <v>Valor decimal</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>1.3</v>
-      </c>
-      <c r="G24">
-        <v>12.600000000000001</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -47784,25 +47784,25 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>Probable NF</v>
+      </c>
+      <c r="B25" t="str">
         <v>Dislocada</v>
       </c>
-      <c r="B25">
+      <c r="C25">
         <v>25</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>1</v>
       </c>
-      <c r="D25" t="str">
-        <v>A</v>
-      </c>
-      <c r="E25">
+      <c r="E25" t="str">
+        <v>A</v>
+      </c>
+      <c r="F25">
         <v>0.1</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
         <v>GRUPOS</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Probable NF</v>
       </c>
       <c r="H25">
         <v>0.9</v>
@@ -47812,26 +47812,26 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
+      <c r="A26">
+        <v>11.100000000000001</v>
+      </c>
+      <c r="B26" t="str">
         <v>Dominada adelante a Lsit</v>
       </c>
-      <c r="B26">
+      <c r="C26">
         <v>2</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>3</v>
       </c>
-      <c r="D26" t="str">
+      <c r="E26" t="str">
         <v>B</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>0.2</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>1.3</v>
-      </c>
-      <c r="G26">
-        <v>11.100000000000001</v>
       </c>
       <c r="H26">
         <v>0.9</v>
@@ -47842,22 +47842,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
+        <v/>
+      </c>
+      <c r="B27" t="str">
         <v>Rodada extendida adel</v>
       </c>
-      <c r="B27">
+      <c r="C27">
         <v>7</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>1</v>
       </c>
-      <c r="D27" t="str">
-        <v>A</v>
-      </c>
-      <c r="E27">
+      <c r="E27" t="str">
+        <v>A</v>
+      </c>
+      <c r="F27">
         <v>0.1</v>
-      </c>
-      <c r="F27" t="str">
-        <v/>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -47871,22 +47871,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
+        <v/>
+      </c>
+      <c r="B28" t="str">
         <v>Inglesa</v>
       </c>
-      <c r="B28">
+      <c r="C28">
         <v>31</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>1</v>
       </c>
-      <c r="D28" t="str">
-        <v>A</v>
-      </c>
-      <c r="E28">
+      <c r="E28" t="str">
+        <v>A</v>
+      </c>
+      <c r="F28">
         <v>0.1</v>
-      </c>
-      <c r="F28" t="str">
-        <v/>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -47900,22 +47900,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
+        <v/>
+      </c>
+      <c r="B29" t="str">
         <v>L sit</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>1</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>2</v>
       </c>
-      <c r="D29" t="str">
-        <v>A</v>
-      </c>
-      <c r="E29">
+      <c r="E29" t="str">
+        <v>A</v>
+      </c>
+      <c r="F29">
         <v>0.1</v>
-      </c>
-      <c r="F29" t="str">
-        <v/>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -47929,22 +47929,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
+        <v/>
+      </c>
+      <c r="B30" t="str">
         <v>Kato</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>26</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>2</v>
       </c>
-      <c r="D30" t="str">
+      <c r="E30" t="str">
         <v>B</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>0.2</v>
-      </c>
-      <c r="F30" t="str">
-        <v/>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -47958,25 +47958,25 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v/>
+      </c>
+      <c r="B31" t="str">
         <v>Molino sost</v>
       </c>
-      <c r="B31">
+      <c r="C31">
         <v>62</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>1</v>
       </c>
-      <c r="D31" t="str">
+      <c r="E31" t="str">
         <v>C</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>0.3</v>
       </c>
-      <c r="F31" t="str">
+      <c r="G31" t="str">
         <v>BPP</v>
-      </c>
-      <c r="G31" t="str">
-        <v/>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -47987,22 +47987,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
+        <v/>
+      </c>
+      <c r="B32" t="str">
         <v xml:space="preserve">Doble atras en c </v>
       </c>
-      <c r="B32">
+      <c r="C32">
         <v>32</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>4</v>
       </c>
-      <c r="D32" t="str">
+      <c r="E32" t="str">
         <v>B</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>0.2</v>
-      </c>
-      <c r="F32" t="str">
-        <v/>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -48016,16 +48016,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
+        <v/>
+      </c>
+      <c r="B33" t="str">
         <v>SALTO DE CABALLO</v>
       </c>
-      <c r="B33" t="str">
-        <v/>
-      </c>
       <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
         <v>FER</v>
-      </c>
-      <c r="D33" t="str">
-        <v/>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -48045,26 +48045,26 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
+        <v>Probable NF</v>
+      </c>
+      <c r="B34" t="str">
         <v>NOMBRE</v>
       </c>
-      <c r="B34" t="str">
+      <c r="C34" t="str">
         <v>NÚM DE ID</v>
       </c>
-      <c r="C34" t="str">
+      <c r="D34" t="str">
         <v>GRUPO</v>
       </c>
-      <c r="D34" t="str">
+      <c r="E34" t="str">
         <v>VALOR</v>
       </c>
-      <c r="E34" t="str">
+      <c r="F34" t="str">
         <v>NOTA D</v>
       </c>
-      <c r="F34" t="str">
+      <c r="G34" t="str">
         <v>SALTOS</v>
       </c>
-      <c r="G34" t="str">
-        <v>Probable NF</v>
-      </c>
       <c r="H34" t="str">
         <v/>
       </c>
@@ -48073,26 +48073,26 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
+      <c r="A35">
+        <v>10.7</v>
+      </c>
+      <c r="B35" t="str">
         <v>Tsukahara en carpa</v>
       </c>
-      <c r="B35">
+      <c r="C35">
         <v>308</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>3</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>2</v>
       </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-      <c r="F35">
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35">
         <v>12</v>
-      </c>
-      <c r="G35">
-        <v>10.7</v>
       </c>
       <c r="H35">
         <v>0.6</v>
@@ -48103,25 +48103,25 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
+        <v>NP</v>
+      </c>
+      <c r="B36" t="str">
         <v>PARALELAS</v>
       </c>
-      <c r="B36" t="str">
-        <v/>
-      </c>
       <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
         <v>FER</v>
       </c>
-      <c r="D36" t="str">
-        <v/>
-      </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
         <v>NOTA D</v>
-      </c>
-      <c r="G36" t="str">
-        <v>NP</v>
       </c>
       <c r="H36" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -48131,26 +48131,26 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
+      <c r="A37">
+        <v>12.299999999999999</v>
+      </c>
+      <c r="B37" t="str">
         <v>NOMBRE</v>
       </c>
-      <c r="B37" t="str">
+      <c r="C37" t="str">
         <v>NÚM DE ID</v>
       </c>
-      <c r="C37" t="str">
+      <c r="D37" t="str">
         <v>GRUPO</v>
       </c>
-      <c r="D37" t="str">
+      <c r="E37" t="str">
         <v>VALOR</v>
       </c>
-      <c r="E37" t="str">
+      <c r="F37" t="str">
         <v>Valor decimal</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>1.0999999999999999</v>
-      </c>
-      <c r="G37">
-        <v>12.299999999999999</v>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -48161,25 +48161,25 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
+        <v>Probable NF</v>
+      </c>
+      <c r="B38" t="str">
         <v xml:space="preserve">Alemana </v>
       </c>
-      <c r="B38">
+      <c r="C38">
         <v>73</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>3</v>
       </c>
-      <c r="D38" t="str">
-        <v>A</v>
-      </c>
-      <c r="E38">
+      <c r="E38" t="str">
+        <v>A</v>
+      </c>
+      <c r="F38">
         <v>0.1</v>
       </c>
-      <c r="F38" t="str">
+      <c r="G38" t="str">
         <v>GRUPOS</v>
-      </c>
-      <c r="G38" t="str">
-        <v>Probable NF</v>
       </c>
       <c r="H38">
         <v>0.8</v>
@@ -48189,26 +48189,26 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
+      <c r="A39">
+        <v>10.799999999999999</v>
+      </c>
+      <c r="B39" t="str">
         <v>L-sit</v>
       </c>
-      <c r="B39">
+      <c r="C39">
         <v>7</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>2</v>
       </c>
-      <c r="D39" t="str">
-        <v>A</v>
-      </c>
-      <c r="E39">
+      <c r="E39" t="str">
+        <v>A</v>
+      </c>
+      <c r="F39">
         <v>0.1</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>1.2</v>
-      </c>
-      <c r="G39">
-        <v>10.799999999999999</v>
       </c>
       <c r="H39">
         <v>0.7</v>
@@ -48219,22 +48219,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
+        <v/>
+      </c>
+      <c r="B40" t="str">
         <v>Kato</v>
       </c>
-      <c r="B40">
+      <c r="C40">
         <v>8</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>2</v>
       </c>
-      <c r="D40" t="str">
+      <c r="E40" t="str">
         <v>B</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>0.2</v>
-      </c>
-      <c r="F40" t="str">
-        <v/>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -48248,22 +48248,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
+        <v/>
+      </c>
+      <c r="B41" t="str">
         <v>Moy extendido</v>
       </c>
-      <c r="B41">
+      <c r="C41">
         <v>15</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>3</v>
       </c>
-      <c r="D41" t="str">
+      <c r="E41" t="str">
         <v>C</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>0.3</v>
-      </c>
-      <c r="F41" t="str">
-        <v/>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -48277,22 +48277,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
+        <v/>
+      </c>
+      <c r="B42" t="str">
         <v>Vuelo</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>1</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>2</v>
       </c>
-      <c r="D42" t="str">
-        <v>A</v>
-      </c>
-      <c r="E42">
+      <c r="E42" t="str">
+        <v>A</v>
+      </c>
+      <c r="F42">
         <v>0.1</v>
-      </c>
-      <c r="F42" t="str">
-        <v/>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -48306,22 +48306,22 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
+        <v/>
+      </c>
+      <c r="B43" t="str">
         <v>Cambio</v>
       </c>
-      <c r="B43">
+      <c r="C43">
         <v>91</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>2</v>
       </c>
-      <c r="D43" t="str">
-        <v>A</v>
-      </c>
-      <c r="E43">
+      <c r="E43" t="str">
+        <v>A</v>
+      </c>
+      <c r="F43">
         <v>0.1</v>
-      </c>
-      <c r="F43" t="str">
-        <v/>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -48335,25 +48335,25 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
+        <v/>
+      </c>
+      <c r="B44" t="str">
         <v xml:space="preserve">Braq Subida de pecho </v>
-      </c>
-      <c r="B44">
-        <v>1</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
-      <c r="D44" t="str">
-        <v>A</v>
-      </c>
-      <c r="E44">
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="str">
+        <v>A</v>
+      </c>
+      <c r="F44">
         <v>0.1</v>
       </c>
-      <c r="F44" t="str">
+      <c r="G44" t="str">
         <v>BPP</v>
-      </c>
-      <c r="G44" t="str">
-        <v/>
       </c>
       <c r="H44">
         <v>0.8</v>
@@ -48364,22 +48364,22 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
+        <v/>
+      </c>
+      <c r="B45" t="str">
         <v>Mortal adelante carp lat</v>
       </c>
-      <c r="B45">
+      <c r="C45">
         <v>1</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>4</v>
       </c>
-      <c r="D45" t="str">
-        <v>A</v>
-      </c>
-      <c r="E45">
+      <c r="E45" t="str">
+        <v>A</v>
+      </c>
+      <c r="F45">
         <v>0.1</v>
-      </c>
-      <c r="F45" t="str">
-        <v/>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -48393,25 +48393,25 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
+        <v>NP</v>
+      </c>
+      <c r="B46" t="str">
         <v>FIJA</v>
       </c>
-      <c r="B46" t="str">
-        <v/>
-      </c>
       <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
         <v>FER</v>
       </c>
-      <c r="D46" t="str">
-        <v/>
-      </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
         <v>NOTA D</v>
-      </c>
-      <c r="G46" t="str">
-        <v>NP</v>
       </c>
       <c r="H46" t="str">
         <v>ETAPA DE ELEMENTO</v>
@@ -48421,26 +48421,26 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
+      <c r="A47">
+        <v>12.3</v>
+      </c>
+      <c r="B47" t="str">
         <v>NOMBRE</v>
       </c>
-      <c r="B47" t="str">
+      <c r="C47" t="str">
         <v>NÚM DE ID</v>
       </c>
-      <c r="C47" t="str">
+      <c r="D47" t="str">
         <v>GRUPO</v>
       </c>
-      <c r="D47" t="str">
+      <c r="E47" t="str">
         <v>VALOR</v>
       </c>
-      <c r="E47" t="str">
+      <c r="F47" t="str">
         <v>Valor decimal</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>1</v>
-      </c>
-      <c r="G47">
-        <v>12</v>
       </c>
       <c r="H47" t="str">
         <v/>
@@ -48451,25 +48451,25 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Alemana</v>
-      </c>
-      <c r="B48">
-        <v>1</v>
+        <v>Probable NF</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Torera</v>
       </c>
       <c r="C48">
-        <v>3</v>
-      </c>
-      <c r="D48" t="str">
-        <v>A</v>
-      </c>
-      <c r="E48">
-        <v>0.1</v>
-      </c>
-      <c r="F48" t="str">
+        <v>25</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48" t="str">
+        <v>B</v>
+      </c>
+      <c r="F48">
+        <v>0.2</v>
+      </c>
+      <c r="G48" t="str">
         <v>GRUPOS</v>
-      </c>
-      <c r="G48" t="str">
-        <v>Probable NF</v>
       </c>
       <c r="H48">
         <v>0.8</v>
@@ -48479,26 +48479,26 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
-        <v>Gigante</v>
-      </c>
-      <c r="B49">
-        <v>13</v>
+      <c r="A49">
+        <v>10.8</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Alemana</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
-      <c r="D49" t="str">
-        <v>A</v>
-      </c>
-      <c r="E49">
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49" t="str">
+        <v>A</v>
+      </c>
+      <c r="F49">
         <v>0.1</v>
       </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
       <c r="G49">
-        <v>10.5</v>
+        <v>1.3</v>
       </c>
       <c r="H49">
         <v>0.8</v>
@@ -48509,22 +48509,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Gigante Saltado</v>
-      </c>
-      <c r="B50">
-        <v>44</v>
+        <v/>
+      </c>
+      <c r="B50" t="str">
+        <v>Gigante</v>
       </c>
       <c r="C50">
+        <v>13</v>
+      </c>
+      <c r="D50">
         <v>1</v>
       </c>
-      <c r="D50" t="str">
-        <v>B</v>
-      </c>
-      <c r="E50">
-        <v>0.2</v>
-      </c>
-      <c r="F50" t="str">
-        <v/>
+      <c r="E50" t="str">
+        <v>A</v>
+      </c>
+      <c r="F50">
+        <v>0.1</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -48538,22 +48538,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
+        <v/>
+      </c>
+      <c r="B51" t="str">
         <v>Salvada</v>
       </c>
-      <c r="B51">
+      <c r="C51">
         <v>25</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>3</v>
       </c>
-      <c r="D51" t="str">
-        <v>A</v>
-      </c>
-      <c r="E51">
+      <c r="E51" t="str">
+        <v>A</v>
+      </c>
+      <c r="F51">
         <v>0.1</v>
-      </c>
-      <c r="F51" t="str">
-        <v/>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -48567,22 +48567,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
+        <v/>
+      </c>
+      <c r="B52" t="str">
         <v>Cambio directo</v>
       </c>
-      <c r="B52">
+      <c r="C52">
         <v>37</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>1</v>
       </c>
-      <c r="D52" t="str">
-        <v>A</v>
-      </c>
-      <c r="E52">
+      <c r="E52" t="str">
+        <v>A</v>
+      </c>
+      <c r="F52">
         <v>0.1</v>
-      </c>
-      <c r="F52" t="str">
-        <v/>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -48596,22 +48596,22 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
+        <v/>
+      </c>
+      <c r="B53" t="str">
         <v>Molino</v>
       </c>
-      <c r="B53">
+      <c r="C53">
         <v>13</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>1</v>
       </c>
-      <c r="D53" t="str">
-        <v>A</v>
-      </c>
-      <c r="E53">
+      <c r="E53" t="str">
+        <v>A</v>
+      </c>
+      <c r="F53">
         <v>0.1</v>
-      </c>
-      <c r="F53" t="str">
-        <v/>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -48625,25 +48625,25 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
+        <v/>
+      </c>
+      <c r="B54" t="str">
         <v>Cambio sencillo</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <v>7</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>1</v>
       </c>
-      <c r="D54" t="str">
-        <v>A</v>
-      </c>
-      <c r="E54">
+      <c r="E54" t="str">
+        <v>A</v>
+      </c>
+      <c r="F54">
         <v>0.1</v>
       </c>
-      <c r="F54" t="str">
+      <c r="G54" t="str">
         <v>BPP</v>
-      </c>
-      <c r="G54" t="str">
-        <v/>
       </c>
       <c r="H54">
         <v>0.8</v>
@@ -48654,22 +48654,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
+        <v/>
+      </c>
+      <c r="B55" t="str">
         <v>Doble agrupado atras</v>
       </c>
-      <c r="B55">
+      <c r="C55">
         <v>32</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>4</v>
       </c>
-      <c r="D55" t="str">
+      <c r="E55" t="str">
         <v>B</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>0.2</v>
-      </c>
-      <c r="F55" t="str">
-        <v/>
       </c>
       <c r="G55" t="str">
         <v/>
